--- a/artfynd/A 25913-2026 artfynd.xlsx
+++ b/artfynd/A 25913-2026 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY4"/>
+  <dimension ref="A1:AY5"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -675,61 +675,57 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>89916028</v>
+        <v>127916035</v>
       </c>
       <c r="B2" t="n">
-        <v>56311</v>
-      </c>
-      <c r="C2" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>56845</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E2" t="n">
-        <v>100067</v>
+        <v>100053</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Havsörn</t>
+          <t>Igelkott</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Haliaeetus albicilla</t>
+          <t>Erinaceus europaeus</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>Linnaeus, 1758</t>
         </is>
       </c>
       <c r="I2" t="inlineStr">
         <is>
-          <t>2</t>
-        </is>
-      </c>
-      <c r="K2" t="inlineStr"/>
-      <c r="L2" t="inlineStr"/>
-      <c r="M2" t="inlineStr"/>
-      <c r="N2" t="inlineStr"/>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="N2" t="inlineStr">
+        <is>
+          <t>observerad</t>
+        </is>
+      </c>
       <c r="P2" t="inlineStr">
         <is>
-          <t>Kraftledningsgata, NV Porshanken, Upl</t>
+          <t>Roslagsleden, 761 63 Norrtälje, Upl</t>
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>708082.1767161237</v>
+        <v>708209</v>
       </c>
       <c r="R2" t="n">
-        <v>6633101.946861479</v>
+        <v>6633045</v>
       </c>
       <c r="S2" t="n">
-        <v>50</v>
+        <v>1</v>
       </c>
       <c r="T2" t="inlineStr">
         <is>
@@ -753,27 +749,22 @@
       </c>
       <c r="Y2" t="inlineStr">
         <is>
-          <t>2021-01-02</t>
+          <t>2025-08-08</t>
         </is>
       </c>
       <c r="Z2" t="inlineStr">
         <is>
-          <t>12:05</t>
+          <t>15:31</t>
         </is>
       </c>
       <c r="AA2" t="inlineStr">
         <is>
-          <t>2021-01-02</t>
+          <t>2025-08-08</t>
         </is>
       </c>
       <c r="AB2" t="inlineStr">
         <is>
-          <t>12:05</t>
-        </is>
-      </c>
-      <c r="AC2" t="inlineStr">
-        <is>
-          <t>Inte adulta. En sågs förmodligen lite tidigare vid telemasten.</t>
+          <t>15:31</t>
         </is>
       </c>
       <c r="AD2" t="b">
@@ -788,77 +779,72 @@
       <c r="AT2" t="inlineStr"/>
       <c r="AW2" t="inlineStr">
         <is>
-          <t>Magnus Bladlund</t>
+          <t>Johan Möller</t>
         </is>
       </c>
       <c r="AX2" t="inlineStr">
         <is>
-          <t>Magnus Bladlund</t>
-        </is>
-      </c>
-      <c r="AY2" t="inlineStr"/>
+          <t>Via Johan Möller</t>
+        </is>
+      </c>
+      <c r="AY2" t="inlineStr">
+        <is>
+          <t>WWF - Tillsammans för Sveriges igelkottar</t>
+        </is>
+      </c>
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>98492808</v>
+        <v>89916028</v>
       </c>
       <c r="B3" t="n">
-        <v>56540</v>
-      </c>
-      <c r="C3" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>57899</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E3" t="n">
-        <v>103021</v>
+        <v>100067</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Talltita</t>
+          <t>Havsörn</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Poecile montanus</t>
+          <t>Haliaeetus albicilla</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(Conrad von Baldenstein, 1827)</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I3" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>2</t>
         </is>
       </c>
       <c r="K3" t="inlineStr"/>
       <c r="L3" t="inlineStr"/>
-      <c r="M3" t="inlineStr">
-        <is>
-          <t>spel/sång</t>
-        </is>
-      </c>
+      <c r="M3" t="inlineStr"/>
       <c r="N3" t="inlineStr"/>
       <c r="P3" t="inlineStr">
         <is>
-          <t>Norrtälje, Upl</t>
+          <t>Kraftledningsgata, NV Porshanken, Upl</t>
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>708278.152346731</v>
+        <v>708082</v>
       </c>
       <c r="R3" t="n">
-        <v>6633058.940737593</v>
+        <v>6633102</v>
       </c>
       <c r="S3" t="n">
-        <v>25</v>
+        <v>50</v>
       </c>
       <c r="T3" t="inlineStr">
         <is>
@@ -882,22 +868,27 @@
       </c>
       <c r="Y3" t="inlineStr">
         <is>
-          <t>2022-02-06</t>
+          <t>2021-01-02</t>
         </is>
       </c>
       <c r="Z3" t="inlineStr">
         <is>
-          <t>12:35</t>
+          <t>12:05</t>
         </is>
       </c>
       <c r="AA3" t="inlineStr">
         <is>
-          <t>2022-02-06</t>
+          <t>2021-01-02</t>
         </is>
       </c>
       <c r="AB3" t="inlineStr">
         <is>
-          <t>12:35</t>
+          <t>12:05</t>
+        </is>
+      </c>
+      <c r="AC3" t="inlineStr">
+        <is>
+          <t>Inte adulta. En sågs förmodligen lite tidigare vid telemasten.</t>
         </is>
       </c>
       <c r="AD3" t="b">
@@ -924,10 +915,10 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>127916035</v>
+        <v>98492808</v>
       </c>
       <c r="B4" t="n">
-        <v>56620</v>
+        <v>58114</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -935,21 +926,21 @@
         </is>
       </c>
       <c r="E4" t="n">
-        <v>100053</v>
+        <v>103021</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Igelkott</t>
+          <t>Talltita</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Erinaceus europaeus</t>
+          <t>Poecile montanus</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>Linnaeus, 1758</t>
+          <t>(Conrad von Baldenstein, 1827)</t>
         </is>
       </c>
       <c r="I4" t="inlineStr">
@@ -957,24 +948,27 @@
           <t>1</t>
         </is>
       </c>
-      <c r="N4" t="inlineStr">
-        <is>
-          <t>observerad</t>
-        </is>
-      </c>
+      <c r="K4" t="inlineStr"/>
+      <c r="L4" t="inlineStr"/>
+      <c r="M4" t="inlineStr">
+        <is>
+          <t>spel/sång</t>
+        </is>
+      </c>
+      <c r="N4" t="inlineStr"/>
       <c r="P4" t="inlineStr">
         <is>
-          <t>Roslagsleden, 761 63 Norrtälje, Upl</t>
+          <t>Norrtälje, Upl</t>
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>708209</v>
+        <v>708278</v>
       </c>
       <c r="R4" t="n">
-        <v>6633045</v>
+        <v>6633059</v>
       </c>
       <c r="S4" t="n">
-        <v>1</v>
+        <v>25</v>
       </c>
       <c r="T4" t="inlineStr">
         <is>
@@ -998,22 +992,22 @@
       </c>
       <c r="Y4" t="inlineStr">
         <is>
-          <t>2025-08-08</t>
+          <t>2022-02-06</t>
         </is>
       </c>
       <c r="Z4" t="inlineStr">
         <is>
-          <t>15:31</t>
+          <t>12:35</t>
         </is>
       </c>
       <c r="AA4" t="inlineStr">
         <is>
-          <t>2025-08-08</t>
+          <t>2022-02-06</t>
         </is>
       </c>
       <c r="AB4" t="inlineStr">
         <is>
-          <t>15:31</t>
+          <t>12:35</t>
         </is>
       </c>
       <c r="AD4" t="b">
@@ -1028,19 +1022,130 @@
       <c r="AT4" t="inlineStr"/>
       <c r="AW4" t="inlineStr">
         <is>
-          <t>Johan Möller</t>
+          <t>Magnus Bladlund</t>
         </is>
       </c>
       <c r="AX4" t="inlineStr">
         <is>
-          <t>Johan Möller</t>
-        </is>
-      </c>
-      <c r="AY4" t="inlineStr">
-        <is>
-          <t>WWF - Tillsammans för Sveriges igelkottar</t>
-        </is>
-      </c>
+          <t>Magnus Bladlund</t>
+        </is>
+      </c>
+      <c r="AY4" t="inlineStr"/>
+    </row>
+    <row r="5">
+      <c r="A5" t="n">
+        <v>98492811</v>
+      </c>
+      <c r="B5" t="n">
+        <v>58636</v>
+      </c>
+      <c r="D5" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E5" t="n">
+        <v>103044</v>
+      </c>
+      <c r="F5" t="inlineStr">
+        <is>
+          <t>Grönsiska</t>
+        </is>
+      </c>
+      <c r="G5" t="inlineStr">
+        <is>
+          <t>Spinus spinus</t>
+        </is>
+      </c>
+      <c r="H5" t="inlineStr">
+        <is>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I5" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="K5" t="inlineStr"/>
+      <c r="L5" t="inlineStr"/>
+      <c r="M5" t="inlineStr"/>
+      <c r="N5" t="inlineStr"/>
+      <c r="P5" t="inlineStr">
+        <is>
+          <t>Norrtälje, Upl</t>
+        </is>
+      </c>
+      <c r="Q5" t="n">
+        <v>708278</v>
+      </c>
+      <c r="R5" t="n">
+        <v>6633059</v>
+      </c>
+      <c r="S5" t="n">
+        <v>25</v>
+      </c>
+      <c r="T5" t="inlineStr">
+        <is>
+          <t>Stockholm</t>
+        </is>
+      </c>
+      <c r="U5" t="inlineStr">
+        <is>
+          <t>Norrtälje</t>
+        </is>
+      </c>
+      <c r="V5" t="inlineStr">
+        <is>
+          <t>Uppland</t>
+        </is>
+      </c>
+      <c r="W5" t="inlineStr">
+        <is>
+          <t>Estuna</t>
+        </is>
+      </c>
+      <c r="Y5" t="inlineStr">
+        <is>
+          <t>2022-02-06</t>
+        </is>
+      </c>
+      <c r="Z5" t="inlineStr">
+        <is>
+          <t>12:35</t>
+        </is>
+      </c>
+      <c r="AA5" t="inlineStr">
+        <is>
+          <t>2022-02-06</t>
+        </is>
+      </c>
+      <c r="AB5" t="inlineStr">
+        <is>
+          <t>12:35</t>
+        </is>
+      </c>
+      <c r="AD5" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE5" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG5" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT5" t="inlineStr"/>
+      <c r="AW5" t="inlineStr">
+        <is>
+          <t>Magnus Bladlund</t>
+        </is>
+      </c>
+      <c r="AX5" t="inlineStr">
+        <is>
+          <t>Magnus Bladlund</t>
+        </is>
+      </c>
+      <c r="AY5" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/artfynd/A 25913-2026 artfynd.xlsx
+++ b/artfynd/A 25913-2026 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY5"/>
+  <dimension ref="A1:AZ5"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -672,6 +672,11 @@
           <t>Projektnamn</t>
         </is>
       </c>
+      <c r="AZ1" t="inlineStr">
+        <is>
+          <t>Artportalenlänk</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2" t="n">
@@ -790,6 +795,11 @@
       <c r="AY2" t="inlineStr">
         <is>
           <t>WWF - Tillsammans för Sveriges igelkottar</t>
+        </is>
+      </c>
+      <c r="AZ2" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/127916035</t>
         </is>
       </c>
     </row>
@@ -912,6 +922,11 @@
         </is>
       </c>
       <c r="AY3" t="inlineStr"/>
+      <c r="AZ3" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/89916028</t>
+        </is>
+      </c>
     </row>
     <row r="4">
       <c r="A4" t="n">
@@ -1031,6 +1046,11 @@
         </is>
       </c>
       <c r="AY4" t="inlineStr"/>
+      <c r="AZ4" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/98492808</t>
+        </is>
+      </c>
     </row>
     <row r="5">
       <c r="A5" t="n">
@@ -1146,8 +1166,19 @@
         </is>
       </c>
       <c r="AY5" t="inlineStr"/>
+      <c r="AZ5" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/98492811</t>
+        </is>
+      </c>
     </row>
   </sheetData>
+  <hyperlinks>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ2" r:id="rId1"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ3" r:id="rId2"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ4" r:id="rId3"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ5" r:id="rId4"/>
+  </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>